--- a/questions.xlsx
+++ b/questions.xlsx
@@ -437,7 +437,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
